--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.852820641171906</v>
+        <v>0.3010833541904348</v>
       </c>
       <c r="D2" t="n">
-        <v>2.732942595385011</v>
+        <v>0.4441031717500643</v>
       </c>
       <c r="E2" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F2" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.78028083272154</v>
+        <v>6.301795635317252</v>
       </c>
       <c r="D3" t="n">
-        <v>39.29790763437818</v>
+        <v>6.385909990586454</v>
       </c>
       <c r="E3" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F3" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.5041145993031</v>
+        <v>2.194418622386754</v>
       </c>
       <c r="D4" t="n">
-        <v>53.17354144573737</v>
+        <v>8.640700484932323</v>
       </c>
       <c r="E4" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F4" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.47754490405309</v>
+        <v>2.677601046908628</v>
       </c>
       <c r="D5" t="n">
-        <v>16.93722100721201</v>
+        <v>2.752298413671951</v>
       </c>
       <c r="E5" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F5" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.29790364243404</v>
+        <v>4.110909341895531</v>
       </c>
       <c r="D6" t="n">
-        <v>44.8074671782177</v>
+        <v>7.281213416460377</v>
       </c>
       <c r="E6" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F6" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.28717091191532</v>
+        <v>1.83416527318624</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93960128874244</v>
+        <v>7.465185209420646</v>
       </c>
       <c r="E7" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F7" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.89933085930118</v>
+        <v>3.233641264636441</v>
       </c>
       <c r="D8" t="n">
-        <v>19.6380371596255</v>
+        <v>3.191181038439144</v>
       </c>
       <c r="E8" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F8" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.16327700059092</v>
+        <v>1.976532512596025</v>
       </c>
       <c r="D9" t="n">
-        <v>12.4328017706217</v>
+        <v>2.020330287726027</v>
       </c>
       <c r="E9" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F9" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.47059696728294</v>
+        <v>5.113972007183478</v>
       </c>
       <c r="D10" t="n">
-        <v>31.66090105238863</v>
+        <v>5.144896421013153</v>
       </c>
       <c r="E10" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F10" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.30726735095139</v>
+        <v>5.737430944529601</v>
       </c>
       <c r="D11" t="n">
-        <v>26.47423495774861</v>
+        <v>4.302063180634149</v>
       </c>
       <c r="E11" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F11" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.93087862053395</v>
+        <v>2.751267775836768</v>
       </c>
       <c r="D12" t="n">
-        <v>16.84434749807642</v>
+        <v>2.737206468437418</v>
       </c>
       <c r="E12" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F12" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.04235034902651</v>
+        <v>6.506881931716808</v>
       </c>
       <c r="D13" t="n">
-        <v>39.48427965091186</v>
+        <v>6.416195443273177</v>
       </c>
       <c r="E13" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F13" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.86426343848342</v>
+        <v>6.802942808753556</v>
       </c>
       <c r="D14" t="n">
-        <v>41.327765679364</v>
+        <v>6.71576192289665</v>
       </c>
       <c r="E14" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F14" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.69165725351733</v>
+        <v>9.374894303696568</v>
       </c>
       <c r="D15" t="n">
-        <v>57.76912193698067</v>
+        <v>9.387482314759358</v>
       </c>
       <c r="E15" t="n">
-        <v>14.85827941383012</v>
+        <v>2.414470404747394</v>
       </c>
       <c r="F15" t="n">
-        <v>15.91597622285867</v>
+        <v>2.586346136214534</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
